--- a/ksoft/docs/records/Receipt_Via_Transp_Enum.xlsx
+++ b/ksoft/docs/records/Receipt_Via_Transp_Enum.xlsx
@@ -1426,13 +1426,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF16BBC4-A1E0-48DC-A5F6-843621D6FAD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0348AA04-D8D2-41F3-9B03-1CE128F18B36}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88E5BB52-3AC3-48DE-92AA-907F5C55E65C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22F5C84A-F023-4B2A-90E5-C19EEB138CFA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7B35245-FEC0-4551-85D3-B5E380022EC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCD64052-98A0-4758-B14A-226B02CEF4E9}"/>
 </file>
--- a/ksoft/docs/records/Receipt_Via_Transp_Enum.xlsx
+++ b/ksoft/docs/records/Receipt_Via_Transp_Enum.xlsx
@@ -1426,13 +1426,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0348AA04-D8D2-41F3-9B03-1CE128F18B36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF16BBC4-A1E0-48DC-A5F6-843621D6FAD3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22F5C84A-F023-4B2A-90E5-C19EEB138CFA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88E5BB52-3AC3-48DE-92AA-907F5C55E65C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCD64052-98A0-4758-B14A-226B02CEF4E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7B35245-FEC0-4551-85D3-B5E380022EC5}"/>
 </file>